--- a/Data/Course Catalog_Master Tracker for 2027_070506_for Schedule Pro OW.xlsx
+++ b/Data/Course Catalog_Master Tracker for 2027_070506_for Schedule Pro OW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/o/SchedulePro2/SchedulePro2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E406B32-1FB6-914E-82F9-4C45A2CE5900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAB7B5A-57BC-7E43-8699-E55099923050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7960" yWindow="-21880" windowWidth="33160" windowHeight="14540" xr2:uid="{D6A8F020-D7CA-42B1-90E3-8F23B7BE620C}"/>
+    <workbookView xWindow="-3220" yWindow="-27780" windowWidth="33660" windowHeight="14580" xr2:uid="{D6A8F020-D7CA-42B1-90E3-8F23B7BE620C}"/>
   </bookViews>
   <sheets>
     <sheet name="Course Catalog for Schedule Pro" sheetId="1" r:id="rId1"/>
@@ -147,7 +147,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -156,12 +156,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Called "Project Management" on the CCR sheet</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Called "Project Management" on the CCR sheet</t>
         </r>
       </text>
     </comment>
@@ -204,7 +213,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -213,12 +222,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Called "Busines Analysis" on the CCR sheet</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Called "Busines Analysis" on the CCR sheet</t>
         </r>
       </text>
     </comment>
